--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487832_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487832_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5621</v>
+        <v>4.4462</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8594</v>
+        <v>4.5379</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2973</v>
+        <v>-0.0917</v>
       </c>
       <c r="G2" t="n">
         <v>4.9942</v>
@@ -610,13 +610,13 @@
         <v>1.2487</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5402</v>
+        <v>-0.6562</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.109</v>
+        <v>-0.4305</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4312</v>
+        <v>-0.2257</v>
       </c>
       <c r="V2" t="n">
         <v>1.9813</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1848</v>
+        <v>4.0571</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0595</v>
+        <v>2.1666</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1254</v>
+        <v>1.8905</v>
       </c>
       <c r="G3" t="n">
         <v>3.6987</v>
@@ -688,13 +688,13 @@
         <v>1.6649</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0352</v>
+        <v>-0.1629</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4972</v>
+        <v>-0.39</v>
       </c>
       <c r="U3" t="n">
-        <v>0.462</v>
+        <v>0.2271</v>
       </c>
       <c r="V3" t="n">
         <v>0.9376</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6135</v>
+        <v>3.9453</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5502</v>
+        <v>2.7645</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0634</v>
+        <v>1.1808</v>
       </c>
       <c r="G4" t="n">
         <v>4.2997</v>
@@ -766,13 +766,13 @@
         <v>1.4568</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4156</v>
+        <v>-0.0838</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5748</v>
+        <v>-0.3605</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1592</v>
+        <v>0.2767</v>
       </c>
       <c r="V4" t="n">
         <v>0.3538</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1632</v>
+        <v>2.3584</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3297</v>
+        <v>2.4369</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1665</v>
+        <v>-0.0785</v>
       </c>
       <c r="G5" t="n">
         <v>1.8311</v>
@@ -844,13 +844,13 @@
         <v>0.4162</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0842</v>
+        <v>0.1111</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3138</v>
+        <v>-0.2067</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2297</v>
+        <v>0.3178</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7171</v>
+        <v>1.9608</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2219</v>
+        <v>1.4362</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4953</v>
+        <v>0.5246</v>
       </c>
       <c r="G6" t="n">
         <v>1.5482</v>
@@ -922,13 +922,13 @@
         <v>1.4568</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7072000000000001</v>
+        <v>-0.4635</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7053</v>
+        <v>-0.491</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0019</v>
+        <v>0.0275</v>
       </c>
       <c r="V6" t="n">
         <v>0.4599</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2953</v>
+        <v>0.9152</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1247</v>
+        <v>1.8033</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8294</v>
+        <v>-0.8881</v>
       </c>
       <c r="G7" t="n">
         <v>1.2498</v>
@@ -1000,13 +1000,13 @@
         <v>1.6649</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7157</v>
+        <v>0.3355</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0215</v>
+        <v>-0.3</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6942</v>
+        <v>0.6355</v>
       </c>
       <c r="V7" t="n">
         <v>-2.3351</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1343</v>
+        <v>-0.5042</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5679</v>
+        <v>-0.9966</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4337</v>
+        <v>0.4924</v>
       </c>
       <c r="G8" t="n">
         <v>-0.8666</v>
@@ -1078,13 +1078,13 @@
         <v>1.4568</v>
       </c>
       <c r="S8" t="n">
-        <v>0.443</v>
+        <v>0.0731</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5434</v>
+        <v>0.1148</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1004</v>
+        <v>-0.0417</v>
       </c>
       <c r="V8" t="n">
         <v>-1.1675</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5554</v>
+        <v>-0.5173</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1513</v>
+        <v>0.3657</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7068</v>
+        <v>-0.8829</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8361</v>
@@ -1156,13 +1156,13 @@
         <v>0.6244</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2198</v>
+        <v>-0.1817</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.2952</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2897</v>
+        <v>0.1136</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1238</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0365</v>
+        <v>-2.0174</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7066</v>
+        <v>-1.5995</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3299</v>
+        <v>-0.4179</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2633</v>
@@ -1234,13 +1234,13 @@
         <v>0.8325</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5245</v>
+        <v>-0.5054</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4319</v>
+        <v>-0.3248</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0926</v>
+        <v>-0.1807</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.2033</v>
+        <v>-6.0375</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1636</v>
+        <v>-3.0565</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.0397</v>
+        <v>-2.981</v>
       </c>
       <c r="G11" t="n">
         <v>-2.3672</v>
@@ -1312,13 +1312,13 @@
         <v>0.6244</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.961</v>
+        <v>-0.7951</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3138</v>
+        <v>-0.2067</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6471</v>
+        <v>-0.5884</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4589</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.6065</v>
+        <v>8.6066</v>
       </c>
       <c r="E12" t="n">
-        <v>9.858599999999999</v>
+        <v>9.858499999999999</v>
       </c>
       <c r="F12" t="n">
         <v>-1.2518</v>
@@ -1390,13 +1390,13 @@
         <v>11.4464</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.329</v>
+        <v>-2.3289</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.8905</v>
+        <v>-2.8906</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5616000000000001</v>
+        <v>0.5616999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-2.3527</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.0217</v>
+        <v>3.0104</v>
       </c>
       <c r="E13" t="n">
-        <v>4.613</v>
+        <v>4.0772</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5914</v>
+        <v>-1.0668</v>
       </c>
       <c r="G13" t="n">
         <v>1.2928</v>
@@ -1468,13 +1468,13 @@
         <v>1.0406</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2107</v>
+        <v>0.1994</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5276999999999999</v>
+        <v>-0.008</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3171</v>
+        <v>0.2075</v>
       </c>
       <c r="V13" t="n">
         <v>0.4776</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2108</v>
+        <v>2.2734</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6677</v>
+        <v>3.2391</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.457</v>
+        <v>-0.9657</v>
       </c>
       <c r="G14" t="n">
         <v>-0.802</v>
@@ -1546,13 +1546,13 @@
         <v>2.0812</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5747</v>
+        <v>0.6374</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4997</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0751</v>
+        <v>0.5663</v>
       </c>
       <c r="V14" t="n">
         <v>1.3975</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7482</v>
+        <v>2.1831</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4587</v>
+        <v>1.7801</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2895</v>
+        <v>0.403</v>
       </c>
       <c r="G15" t="n">
         <v>0.3268</v>
@@ -1624,13 +1624,13 @@
         <v>0.6244</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3706</v>
+        <v>0.0644</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7177</v>
+        <v>-0.3962</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3471</v>
+        <v>0.4606</v>
       </c>
       <c r="V15" t="n">
         <v>1.1675</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8211000000000001</v>
+        <v>0.7282</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4559</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6348</v>
+        <v>-0.0848</v>
       </c>
       <c r="G16" t="n">
         <v>-2.0009</v>
@@ -1702,13 +1702,13 @@
         <v>1.6649</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0301</v>
+        <v>0.9372</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8135</v>
+        <v>0.1705</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2166</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>1.1675</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3537</v>
+        <v>-0.6884</v>
       </c>
       <c r="E17" t="n">
         <v>0.2068</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5605</v>
+        <v>-0.8952</v>
       </c>
       <c r="G17" t="n">
         <v>-2.3265</v>
@@ -1780,13 +1780,13 @@
         <v>1.6649</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2246</v>
+        <v>0.8899</v>
       </c>
       <c r="T17" t="n">
         <v>-0.019</v>
       </c>
       <c r="U17" t="n">
-        <v>1.2436</v>
+        <v>0.9089</v>
       </c>
       <c r="V17" t="n">
         <v>0.1238</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8067</v>
+        <v>-1.1011</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6981000000000001</v>
+        <v>-0.4837</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1086</v>
+        <v>-0.6173999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>-0.524</v>
@@ -1858,13 +1858,13 @@
         <v>0.8325</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0745</v>
+        <v>-0.369</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4972</v>
+        <v>-0.2829</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5774</v>
+        <v>-0.0861</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9896</v>
+        <v>-1.8404</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3976</v>
+        <v>-0.5048</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.592</v>
+        <v>-1.3356</v>
       </c>
       <c r="G19" t="n">
         <v>-2.3458</v>
@@ -1936,13 +1936,13 @@
         <v>0.6244</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7724</v>
+        <v>0.9217</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.6444</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0209</v>
+        <v>0.2773</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6318</v>
+        <v>-2.2864</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1718</v>
+        <v>-0.5288</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.46</v>
+        <v>-1.7576</v>
       </c>
       <c r="G20" t="n">
         <v>-2.1864</v>
@@ -2014,13 +2014,13 @@
         <v>1.4568</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7627</v>
+        <v>1.1081</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7581</v>
+        <v>-0.1152</v>
       </c>
       <c r="U20" t="n">
-        <v>1.5208</v>
+        <v>1.2233</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5838</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3353</v>
+        <v>-3.1107</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7799</v>
+        <v>-2.6728</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5554</v>
+        <v>-0.4379</v>
       </c>
       <c r="G21" t="n">
         <v>-1.2549</v>
@@ -2092,13 +2092,13 @@
         <v>1.0406</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.456</v>
+        <v>-0.2314</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5748</v>
+        <v>-0.4676</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1188</v>
+        <v>0.2362</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5838</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.2913</v>
+        <v>-5.6317</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.1029</v>
+        <v>-4.6743</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1884</v>
+        <v>-0.9574</v>
       </c>
       <c r="G22" t="n">
         <v>-3.4675</v>
@@ -2170,13 +2170,13 @@
         <v>0.4162</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3451</v>
+        <v>0.3144</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.1586</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2421</v>
+        <v>0.473</v>
       </c>
       <c r="V22" t="n">
         <v>-0.8137</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.6066</v>
+        <v>-6.4636</v>
       </c>
       <c r="E23" t="n">
-        <v>1.251799999999999</v>
+        <v>1.2518</v>
       </c>
       <c r="F23" t="n">
-        <v>-9.858599999999999</v>
+        <v>-7.7154</v>
       </c>
       <c r="G23" t="n">
         <v>-13.2884</v>
@@ -2248,13 +2248,13 @@
         <v>11.4465</v>
       </c>
       <c r="S23" t="n">
-        <v>2.329</v>
+        <v>4.4721</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5616000000000003</v>
+        <v>-0.5616</v>
       </c>
       <c r="U23" t="n">
-        <v>2.8905</v>
+        <v>5.0336</v>
       </c>
       <c r="V23" t="n">
         <v>2.3526</v>
